--- a/sitepreview/trust/ValueSet-Participants-UAT.xlsx
+++ b/sitepreview/trust/ValueSet-Participants-UAT.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="83">
   <si>
     <t>Property</t>
   </si>
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.5.0</t>
+    <t>1.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-27T07:32:49+00:00</t>
+    <t>2026-05-19T11:45:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -144,6 +144,9 @@
   </si>
   <si>
     <t>CZE</t>
+  </si>
+  <si>
+    <t>ECU</t>
   </si>
   <si>
     <t>ESP</t>
@@ -564,7 +567,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -797,18 +800,24 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>30</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="B38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
         <v>31</v>
       </c>
-      <c r="B39" t="s" s="2">
-        <v>70</v>
+      <c r="B40" t="s" s="2">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -835,7 +844,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B2" s="2"/>
     </row>
@@ -847,61 +856,61 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B13" s="2"/>
     </row>
